--- a/Hugo/excel/pearson.xlsx
+++ b/Hugo/excel/pearson.xlsx
@@ -393,7 +393,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -421,6 +421,14 @@
       <sz val="11"/>
       <name val="Cambria"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -521,12 +529,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -534,7 +546,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -542,15 +554,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -558,23 +566,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -830,1577 +834,1577 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BK21"/>
+  <dimension ref="A1:BK30"/>
   <sheetFormatPr defaultColWidth="8.3984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="17" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="30" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="34" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="39" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="41" style="0" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="43" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="45" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="47" style="0" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="49" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="51" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="56" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="0" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="0" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="17" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="30" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="34" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="39" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="41" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="43" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="45" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="47" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="49" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="51" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="56" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="1" width="21"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BD1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BE1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BF1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BJ1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BK1" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="2" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>1024</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>102400</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="4" t="n">
         <v>0.319309632857975</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J2" s="4" t="n">
         <v>0.00213457527409025</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="4" t="n">
         <v>0.322634804244652</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L2" s="4" t="n">
         <v>10659.1454115825</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M2" s="4" t="n">
         <v>0.435871455901815</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" s="4" t="n">
         <v>0.0600418002266085</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="O2" s="4" t="n">
         <v>0.10113835145959</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="P2" s="4" t="n">
         <v>0.23265536752851</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="Q2" s="4" t="n">
         <v>0.314791701798416</v>
       </c>
-      <c r="R2" s="3" t="n">
+      <c r="R2" s="4" t="n">
         <v>0.330836544720797</v>
       </c>
-      <c r="S2" s="3" t="n">
+      <c r="S2" s="4" t="n">
         <v>0.342954400933876</v>
       </c>
-      <c r="T2" s="3" t="n">
+      <c r="T2" s="4" t="n">
         <v>0.359832916606878</v>
       </c>
-      <c r="U2" s="3" t="n">
+      <c r="U2" s="4" t="n">
         <v>0.371841625266226</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" s="4" t="n">
         <v>0.375829655675206</v>
       </c>
-      <c r="W2" s="3" t="n">
+      <c r="W2" s="4" t="n">
         <v>17.2180944789384</v>
       </c>
-      <c r="X2" s="3" t="n">
+      <c r="X2" s="4" t="n">
         <v>4.278525670002</v>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="Y2" s="4" t="n">
         <v>0.713087611666999</v>
       </c>
-      <c r="Z2" s="3" t="n">
+      <c r="Z2" s="4" t="n">
         <v>12.756335080686</v>
       </c>
-      <c r="AA2" s="3" t="n">
+      <c r="AA2" s="4" t="n">
         <v>9.75633508068603</v>
       </c>
-      <c r="AB2" s="3" t="n">
+      <c r="AB2" s="4" t="n">
         <v>-2.86682058316547</v>
       </c>
-      <c r="AC2" s="3" t="n">
+      <c r="AC2" s="4" t="n">
         <v>0.999923428775191</v>
       </c>
-      <c r="AD2" s="3" t="n">
+      <c r="AD2" s="4" t="n">
         <v>7.65712248086642E-005</v>
       </c>
-      <c r="AE2" s="3" t="n">
+      <c r="AE2" s="4" t="n">
         <v>0.0138211888897134</v>
       </c>
-      <c r="AF2" s="3" t="n">
+      <c r="AF2" s="4" t="n">
         <v>3.29186942927406</v>
       </c>
-      <c r="AG2" s="3" t="n">
+      <c r="AG2" s="4" t="n">
         <v>-4.00200910037649E-005</v>
       </c>
-      <c r="AH2" s="3" t="n">
+      <c r="AH2" s="4" t="n">
         <v>0.00292160916304402</v>
       </c>
-      <c r="AI2" s="3" t="n">
+      <c r="AI2" s="4" t="n">
         <v>0.0540519265581876</v>
       </c>
-      <c r="AJ2" s="3" t="n">
+      <c r="AJ2" s="4" t="n">
         <v>-327.938999414757</v>
       </c>
-      <c r="AK2" s="3" t="n">
+      <c r="AK2" s="4" t="n">
         <v>35722.6260715848</v>
       </c>
-      <c r="AL2" s="3" t="n">
+      <c r="AL2" s="4" t="n">
         <v>-0.638146745697704</v>
       </c>
-      <c r="AM2" s="3" t="n">
+      <c r="AM2" s="4" t="n">
         <v>0.00299062012412534</v>
       </c>
-      <c r="AN2" s="3" t="n">
+      <c r="AN2" s="4" t="n">
         <v>0.640485666637979</v>
       </c>
-      <c r="AO2" s="3" t="n">
+      <c r="AO2" s="4" t="n">
         <v>0.041548832494044</v>
       </c>
-      <c r="AP2" s="3" t="n">
+      <c r="AP2" s="4" t="n">
         <v>0.00119530528303358</v>
       </c>
-      <c r="AQ2" s="3" t="n">
+      <c r="AQ2" s="4" t="n">
         <v>0.711346573446526</v>
       </c>
-      <c r="AR2" s="3" t="n">
+      <c r="AR2" s="4" t="n">
         <v>0.0540519265581876</v>
       </c>
-      <c r="AS2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" s="3" t="n">
+      <c r="AS2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="4" t="n">
         <v>0.638146745697705</v>
       </c>
-      <c r="AV2" s="3" t="n">
+      <c r="AV2" s="4" t="n">
         <v>0.00299062012412537</v>
       </c>
-      <c r="AW2" s="3" t="n">
+      <c r="AW2" s="4" t="n">
         <v>1.10362509112759</v>
       </c>
-      <c r="AX2" s="3" t="n">
+      <c r="AX2" s="4" t="n">
         <v>0.64048566663798</v>
       </c>
-      <c r="AY2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" s="3" t="n">
+      <c r="AY2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="4" t="n">
         <v>0.0681538922146849</v>
       </c>
-      <c r="BB2" s="3" t="n">
+      <c r="BB2" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="BC2" s="3" t="n">
+      <c r="BC2" s="4" t="n">
         <v>0.104093216909985</v>
       </c>
-      <c r="BD2" s="3" t="n">
+      <c r="BD2" s="4" t="n">
         <v>670.452763522955</v>
       </c>
-      <c r="BE2" s="3" t="n">
+      <c r="BE2" s="4" t="n">
         <v>103.108997145679</v>
       </c>
-      <c r="BF2" s="3" t="n">
+      <c r="BF2" s="4" t="n">
         <v>0.932037967415165</v>
       </c>
-      <c r="BG2" s="3" t="n">
+      <c r="BG2" s="4" t="n">
         <v>0.997403157746151</v>
       </c>
-      <c r="BH2" s="3" t="n">
+      <c r="BH2" s="4" t="n">
         <v>0.347951923889493</v>
       </c>
-      <c r="BI2" s="3" t="n">
+      <c r="BI2" s="4" t="n">
         <v>2.71063095922483</v>
       </c>
-      <c r="BJ2" s="3" t="n">
+      <c r="BJ2" s="4" t="n">
         <v>0.251388825121543</v>
       </c>
-      <c r="BK2" s="4" t="n">
+      <c r="BK2" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="3" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+    <row r="3" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="6" t="n">
         <v>1024</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <v>102400</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="6" t="n">
         <v>0.917204795729018</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="6" t="n">
         <v>0.266633127720621</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="K3" s="6" t="n">
         <v>1.0525672258953</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="L3" s="6" t="n">
         <v>113448.731138963</v>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="M3" s="6" t="n">
         <v>1.62974217438193</v>
       </c>
-      <c r="N3" s="5" t="n">
+      <c r="N3" s="6" t="n">
         <v>0.108104961535274</v>
       </c>
-      <c r="O3" s="5" t="n">
+      <c r="O3" s="6" t="n">
         <v>0.136937722324136</v>
       </c>
-      <c r="P3" s="5" t="n">
+      <c r="P3" s="6" t="n">
         <v>0.162437875507886</v>
       </c>
-      <c r="Q3" s="5" t="n">
+      <c r="Q3" s="6" t="n">
         <v>0.382635707818751</v>
       </c>
-      <c r="R3" s="5" t="n">
+      <c r="R3" s="6" t="n">
         <v>0.999780433703444</v>
       </c>
-      <c r="S3" s="5" t="n">
+      <c r="S3" s="6" t="n">
         <v>1.43555893352252</v>
       </c>
-      <c r="T3" s="5" t="n">
+      <c r="T3" s="6" t="n">
         <v>1.55698126197743</v>
       </c>
-      <c r="U3" s="5" t="n">
+      <c r="U3" s="6" t="n">
         <v>1.58196617549648</v>
       </c>
-      <c r="V3" s="5" t="n">
+      <c r="V3" s="6" t="n">
         <v>1.52163721284665</v>
       </c>
-      <c r="W3" s="5" t="n">
+      <c r="W3" s="6" t="n">
         <v>23.5654655549952</v>
       </c>
-      <c r="X3" s="5" t="n">
+      <c r="X3" s="6" t="n">
         <v>5.68763729929929</v>
       </c>
-      <c r="Y3" s="5" t="n">
+      <c r="Y3" s="6" t="n">
         <v>0.947939549883216</v>
       </c>
-      <c r="Z3" s="5" t="n">
+      <c r="Z3" s="6" t="n">
         <v>1.49731948191515</v>
       </c>
-      <c r="AA3" s="5" t="n">
+      <c r="AA3" s="6" t="n">
         <v>-1.50268051808485</v>
       </c>
-      <c r="AB3" s="5" t="n">
+      <c r="AB3" s="6" t="n">
         <v>-2.91757636045678</v>
       </c>
-      <c r="AC3" s="5" t="n">
+      <c r="AC3" s="6" t="n">
         <v>0.99991591965966</v>
       </c>
-      <c r="AD3" s="5" t="n">
+      <c r="AD3" s="6" t="n">
         <v>8.40803403405031E-005</v>
       </c>
-      <c r="AE3" s="5" t="n">
+      <c r="AE3" s="6" t="n">
         <v>0.0135548198979096</v>
       </c>
-      <c r="AF3" s="5" t="n">
+      <c r="AF3" s="6" t="n">
         <v>3.29604871476114</v>
       </c>
-      <c r="AG3" s="5" t="n">
+      <c r="AG3" s="6" t="n">
         <v>-6.29649748587941E-005</v>
       </c>
-      <c r="AH3" s="5" t="n">
+      <c r="AH3" s="6" t="n">
         <v>0.00573515488086877</v>
       </c>
-      <c r="AI3" s="5" t="n">
+      <c r="AI3" s="6" t="n">
         <v>0.0757308315381313</v>
       </c>
-      <c r="AJ3" s="5" t="n">
+      <c r="AJ3" s="6" t="n">
         <v>-326.957272642576</v>
       </c>
-      <c r="AK3" s="5" t="n">
+      <c r="AK3" s="6" t="n">
         <v>35693.3046855173</v>
       </c>
-      <c r="AL3" s="5" t="n">
+      <c r="AL3" s="6" t="n">
         <v>-0.638118129508681</v>
       </c>
-      <c r="AM3" s="5" t="n">
+      <c r="AM3" s="6" t="n">
         <v>0.00573046065347368</v>
       </c>
-      <c r="AN3" s="5" t="n">
+      <c r="AN3" s="6" t="n">
         <v>0.64259256754271</v>
       </c>
-      <c r="AO3" s="5" t="n">
+      <c r="AO3" s="6" t="n">
         <v>0.0449639553170613</v>
       </c>
-      <c r="AP3" s="5" t="n">
+      <c r="AP3" s="6" t="n">
         <v>0.00371340156770214</v>
       </c>
-      <c r="AQ3" s="5" t="n">
+      <c r="AQ3" s="6" t="n">
         <v>0.883162431916965</v>
       </c>
-      <c r="AR3" s="5" t="n">
+      <c r="AR3" s="6" t="n">
         <v>0.0757308315381313</v>
       </c>
-      <c r="AS3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" s="5" t="n">
+      <c r="AS3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="6" t="n">
         <v>0.638118129508683</v>
       </c>
-      <c r="AV3" s="5" t="n">
+      <c r="AV3" s="6" t="n">
         <v>0.0057304606534737</v>
       </c>
-      <c r="AW3" s="5" t="n">
+      <c r="AW3" s="6" t="n">
         <v>1.17477598769149</v>
       </c>
-      <c r="AX3" s="5" t="n">
+      <c r="AX3" s="6" t="n">
         <v>0.642592567542711</v>
       </c>
-      <c r="AY3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" s="5" t="n">
+      <c r="AY3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="6" t="n">
         <v>0.667018360443324</v>
       </c>
-      <c r="BB3" s="5" t="n">
+      <c r="BB3" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="BC3" s="5" t="n">
+      <c r="BC3" s="6" t="n">
         <v>1.10789776502893</v>
       </c>
-      <c r="BD3" s="5" t="n">
+      <c r="BD3" s="6" t="n">
         <v>616.507065924829</v>
       </c>
-      <c r="BE3" s="5" t="n">
+      <c r="BE3" s="6" t="n">
         <v>336.692333221612</v>
       </c>
-      <c r="BF3" s="5" t="n">
+      <c r="BF3" s="6" t="n">
         <v>2.80833585845983</v>
       </c>
-      <c r="BG3" s="5" t="n">
+      <c r="BG3" s="6" t="n">
         <v>0.999233099498991</v>
       </c>
-      <c r="BH3" s="5" t="n">
+      <c r="BH3" s="6" t="n">
         <v>0.220176490462034</v>
       </c>
-      <c r="BI3" s="5" t="n">
+      <c r="BI3" s="6" t="n">
         <v>8.56076526022612</v>
       </c>
-      <c r="BJ3" s="5" t="n">
+      <c r="BJ3" s="6" t="n">
         <v>0.251903238026505</v>
       </c>
       <c r="BK3" s="6" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="4" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+    <row r="4" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>1024</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="6" t="n">
         <v>102400</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="6" t="n">
         <v>0.917367182676928</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="6" t="n">
         <v>0.266819918551721</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="K4" s="6" t="n">
         <v>1.05279744794729</v>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="L4" s="6" t="n">
         <v>113498.364559803</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="M4" s="6" t="n">
         <v>1.63667021475451</v>
       </c>
-      <c r="N4" s="5" t="n">
+      <c r="N4" s="6" t="n">
         <v>0.105976668793946</v>
       </c>
-      <c r="O4" s="5" t="n">
+      <c r="O4" s="6" t="n">
         <v>0.137358623393341</v>
       </c>
-      <c r="P4" s="5" t="n">
+      <c r="P4" s="6" t="n">
         <v>0.162060718645069</v>
       </c>
-      <c r="Q4" s="5" t="n">
+      <c r="Q4" s="6" t="n">
         <v>0.382092049908371</v>
       </c>
-      <c r="R4" s="5" t="n">
+      <c r="R4" s="6" t="n">
         <v>0.99963197143208</v>
       </c>
-      <c r="S4" s="5" t="n">
+      <c r="S4" s="6" t="n">
         <v>1.43638841639214</v>
       </c>
-      <c r="T4" s="5" t="n">
+      <c r="T4" s="6" t="n">
         <v>1.55744112482819</v>
       </c>
-      <c r="U4" s="5" t="n">
+      <c r="U4" s="6" t="n">
         <v>1.5817463039876</v>
       </c>
-      <c r="V4" s="5" t="n">
+      <c r="V4" s="6" t="n">
         <v>1.53069354596056</v>
       </c>
-      <c r="W4" s="5" t="n">
+      <c r="W4" s="6" t="n">
         <v>23.7750182969941</v>
       </c>
-      <c r="X4" s="5" t="n">
+      <c r="X4" s="6" t="n">
         <v>5.67856938728741</v>
       </c>
-      <c r="Y4" s="5" t="n">
+      <c r="Y4" s="6" t="n">
         <v>0.946428231214568</v>
       </c>
-      <c r="Z4" s="5" t="n">
+      <c r="Z4" s="6" t="n">
         <v>1.49695764238869</v>
       </c>
-      <c r="AA4" s="5" t="n">
+      <c r="AA4" s="6" t="n">
         <v>-1.50304235761131</v>
       </c>
-      <c r="AB4" s="5" t="n">
+      <c r="AB4" s="6" t="n">
         <v>-2.44232646219339</v>
       </c>
-      <c r="AC4" s="5" t="n">
+      <c r="AC4" s="6" t="n">
         <v>0.999893185729768</v>
       </c>
-      <c r="AD4" s="5" t="n">
+      <c r="AD4" s="6" t="n">
         <v>0.000106814270231598</v>
       </c>
-      <c r="AE4" s="5" t="n">
+      <c r="AE4" s="6" t="n">
         <v>0.0279266500004729</v>
       </c>
-      <c r="AF4" s="5" t="n">
+      <c r="AF4" s="6" t="n">
         <v>3.29417950495599</v>
       </c>
-      <c r="AG4" s="5" t="n">
+      <c r="AG4" s="6" t="n">
         <v>8.79854658923454E-005</v>
       </c>
-      <c r="AH4" s="5" t="n">
+      <c r="AH4" s="6" t="n">
         <v>0.00572861891369122</v>
       </c>
-      <c r="AI4" s="5" t="n">
+      <c r="AI4" s="6" t="n">
         <v>0.0756876915695903</v>
       </c>
-      <c r="AJ4" s="5" t="n">
+      <c r="AJ4" s="6" t="n">
         <v>-326.955172658776</v>
       </c>
-      <c r="AK4" s="5" t="n">
+      <c r="AK4" s="6" t="n">
         <v>35693.2848827072</v>
       </c>
-      <c r="AL4" s="5" t="n">
+      <c r="AL4" s="6" t="n">
         <v>-0.638121321620247</v>
       </c>
-      <c r="AM4" s="5" t="n">
+      <c r="AM4" s="6" t="n">
         <v>0.00575832904385723</v>
       </c>
-      <c r="AN4" s="5" t="n">
+      <c r="AN4" s="6" t="n">
         <v>0.642617421293749</v>
       </c>
-      <c r="AO4" s="5" t="n">
+      <c r="AO4" s="6" t="n">
         <v>0.0449970233896303</v>
       </c>
-      <c r="AP4" s="5" t="n">
+      <c r="AP4" s="6" t="n">
         <v>0.0037038945412065</v>
       </c>
-      <c r="AQ4" s="5" t="n">
+      <c r="AQ4" s="6" t="n">
         <v>0.823869073046443</v>
       </c>
-      <c r="AR4" s="5" t="n">
+      <c r="AR4" s="6" t="n">
         <v>0.0756876915695903</v>
       </c>
-      <c r="AS4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" s="5" t="n">
+      <c r="AS4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="6" t="n">
         <v>0.638121321620248</v>
       </c>
-      <c r="AV4" s="5" t="n">
+      <c r="AV4" s="6" t="n">
         <v>0.00575832904385723</v>
       </c>
-      <c r="AW4" s="5" t="n">
+      <c r="AW4" s="6" t="n">
         <v>1.16365410150804</v>
       </c>
-      <c r="AX4" s="5" t="n">
+      <c r="AX4" s="6" t="n">
         <v>0.64261742129375</v>
       </c>
-      <c r="AY4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" s="5" t="n">
+      <c r="AY4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="6" t="n">
         <v>0.667342071495885</v>
       </c>
-      <c r="BB4" s="5" t="n">
+      <c r="BB4" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="BC4" s="5" t="n">
+      <c r="BC4" s="6" t="n">
         <v>1.10838246640432</v>
       </c>
-      <c r="BD4" s="5" t="n">
+      <c r="BD4" s="6" t="n">
         <v>616.536530749461</v>
       </c>
-      <c r="BE4" s="5" t="n">
+      <c r="BE4" s="6" t="n">
         <v>336.766069831617</v>
       </c>
-      <c r="BF4" s="5" t="n">
+      <c r="BF4" s="6" t="n">
         <v>2.70633657605194</v>
       </c>
-      <c r="BG4" s="5" t="n">
+      <c r="BG4" s="6" t="n">
         <v>0.999233656182569</v>
       </c>
-      <c r="BH4" s="5" t="n">
+      <c r="BH4" s="6" t="n">
         <v>0.220728470168548</v>
       </c>
-      <c r="BI4" s="5" t="n">
+      <c r="BI4" s="6" t="n">
         <v>8.55505222849255</v>
       </c>
-      <c r="BJ4" s="5" t="n">
+      <c r="BJ4" s="6" t="n">
         <v>0.251986298487442</v>
       </c>
       <c r="BK4" s="6" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="5" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>1024</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>102400</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="6" t="n">
         <v>0.878785993264063</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="6" t="n">
         <v>0.254356264862942</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="K5" s="6" t="n">
         <v>1.0132231179854</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="L5" s="6" t="n">
         <v>105125.999290373</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="M5" s="6" t="n">
         <v>1.56816529661398</v>
       </c>
-      <c r="N5" s="5" t="n">
+      <c r="N5" s="6" t="n">
         <v>0.0535986853994535</v>
       </c>
-      <c r="O5" s="5" t="n">
+      <c r="O5" s="6" t="n">
         <v>0.0872488613873971</v>
       </c>
-      <c r="P5" s="5" t="n">
+      <c r="P5" s="6" t="n">
         <v>0.111570950446526</v>
       </c>
-      <c r="Q5" s="5" t="n">
+      <c r="Q5" s="6" t="n">
         <v>0.38001912724021</v>
       </c>
-      <c r="R5" s="5" t="n">
+      <c r="R5" s="6" t="n">
         <v>0.960068926427449</v>
       </c>
-      <c r="S5" s="5" t="n">
+      <c r="S5" s="6" t="n">
         <v>1.37923420729556</v>
       </c>
-      <c r="T5" s="5" t="n">
+      <c r="T5" s="6" t="n">
         <v>1.49836038674083</v>
       </c>
-      <c r="U5" s="5" t="n">
+      <c r="U5" s="6" t="n">
         <v>1.52298818701095</v>
       </c>
-      <c r="V5" s="5" t="n">
+      <c r="V5" s="6" t="n">
         <v>1.51456661121453</v>
       </c>
-      <c r="W5" s="5" t="n">
+      <c r="W5" s="6" t="n">
         <v>29.3247540142694</v>
       </c>
-      <c r="X5" s="5" t="n">
+      <c r="X5" s="6" t="n">
         <v>5.72206375834836</v>
       </c>
-      <c r="Y5" s="5" t="n">
+      <c r="Y5" s="6" t="n">
         <v>0.953677293058059</v>
       </c>
-      <c r="Z5" s="5" t="n">
+      <c r="Z5" s="6" t="n">
         <v>1.54887294810781</v>
       </c>
-      <c r="AA5" s="5" t="n">
+      <c r="AA5" s="6" t="n">
         <v>-1.45112705189219</v>
       </c>
-      <c r="AB5" s="5" t="n">
+      <c r="AB5" s="6" t="n">
         <v>2.89116253863892</v>
       </c>
-      <c r="AC5" s="5" t="n">
+      <c r="AC5" s="6" t="n">
         <v>0.999794772882613</v>
       </c>
-      <c r="AD5" s="5" t="n">
+      <c r="AD5" s="6" t="n">
         <v>0.000205227117386756</v>
       </c>
-      <c r="AE5" s="5" t="n">
+      <c r="AE5" s="6" t="n">
         <v>0.016036679145472</v>
       </c>
-      <c r="AF5" s="5" t="n">
+      <c r="AF5" s="6" t="n">
         <v>3.29580523059099</v>
       </c>
-      <c r="AG5" s="5" t="n">
+      <c r="AG5" s="6" t="n">
         <v>7.33659012131748E-005</v>
       </c>
-      <c r="AH5" s="5" t="n">
+      <c r="AH5" s="6" t="n">
         <v>0.00744077165146188</v>
       </c>
-      <c r="AI5" s="5" t="n">
+      <c r="AI5" s="6" t="n">
         <v>0.0862599387550058</v>
       </c>
-      <c r="AJ5" s="5" t="n">
+      <c r="AJ5" s="6" t="n">
         <v>-325.746259359401</v>
       </c>
-      <c r="AK5" s="5" t="n">
+      <c r="AK5" s="6" t="n">
         <v>34746.0540542895</v>
       </c>
-      <c r="AL5" s="5" t="n">
+      <c r="AL5" s="6" t="n">
         <v>-0.632019170808248</v>
       </c>
-      <c r="AM5" s="5" t="n">
+      <c r="AM5" s="6" t="n">
         <v>0.00767705411562334</v>
       </c>
-      <c r="AN5" s="5" t="n">
+      <c r="AN5" s="6" t="n">
         <v>0.638063700883202</v>
       </c>
-      <c r="AO5" s="5" t="n">
+      <c r="AO5" s="6" t="n">
         <v>0.048669003231884</v>
       </c>
-      <c r="AP5" s="5" t="n">
+      <c r="AP5" s="6" t="n">
         <v>0.00507210515843221</v>
       </c>
-      <c r="AQ5" s="5" t="n">
+      <c r="AQ5" s="6" t="n">
         <v>0.688993822841034</v>
       </c>
-      <c r="AR5" s="5" t="n">
+      <c r="AR5" s="6" t="n">
         <v>0.0862599387550058</v>
       </c>
-      <c r="AS5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" s="5" t="n">
+      <c r="AS5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="6" t="n">
         <v>0.632022276168895</v>
       </c>
-      <c r="AV5" s="5" t="n">
+      <c r="AV5" s="6" t="n">
         <v>0.00767312881105923</v>
       </c>
-      <c r="AW5" s="5" t="n">
+      <c r="AW5" s="6" t="n">
         <v>1.27869081105434</v>
       </c>
-      <c r="AX5" s="5" t="n">
+      <c r="AX5" s="6" t="n">
         <v>0.638063700883203</v>
       </c>
-      <c r="AY5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" s="5" t="n">
+      <c r="AY5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="6" t="n">
         <v>0.516607005085379</v>
       </c>
-      <c r="BB5" s="5" t="n">
+      <c r="BB5" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="BC5" s="5" t="n">
+      <c r="BC5" s="6" t="n">
         <v>1.02662108682005</v>
       </c>
-      <c r="BD5" s="5" t="n">
+      <c r="BD5" s="6" t="n">
         <v>515.288044899179</v>
       </c>
-      <c r="BE5" s="5" t="n">
+      <c r="BE5" s="6" t="n">
         <v>324.115054116428</v>
       </c>
-      <c r="BF5" s="5" t="n">
+      <c r="BF5" s="6" t="n">
         <v>1.77492529144656</v>
       </c>
-      <c r="BG5" s="5" t="n">
+      <c r="BG5" s="6" t="n">
         <v>0.999282470692434</v>
       </c>
-      <c r="BH5" s="5" t="n">
+      <c r="BH5" s="6" t="n">
         <v>0.218530325074504</v>
       </c>
-      <c r="BI5" s="5" t="n">
+      <c r="BI5" s="6" t="n">
         <v>7.42398823090603</v>
       </c>
-      <c r="BJ5" s="5" t="n">
+      <c r="BJ5" s="6" t="n">
         <v>0.251292784059302</v>
       </c>
       <c r="BK5" s="6" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="6" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <v>1024</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <v>102400</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="6" t="n">
         <v>0.878566658364212</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J6" s="6" t="n">
         <v>0.254220350125143</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="K6" s="6" t="n">
         <v>1.01296580559978</v>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="L6" s="6" t="n">
         <v>105072.611667395</v>
       </c>
-      <c r="M6" s="5" t="n">
+      <c r="M6" s="6" t="n">
         <v>1.57437358771142</v>
       </c>
-      <c r="N6" s="5" t="n">
+      <c r="N6" s="6" t="n">
         <v>0.0458910713737387</v>
       </c>
-      <c r="O6" s="5" t="n">
+      <c r="O6" s="6" t="n">
         <v>0.0878064648581437</v>
       </c>
-      <c r="P6" s="5" t="n">
+      <c r="P6" s="6" t="n">
         <v>0.111858055081805</v>
       </c>
-      <c r="Q6" s="5" t="n">
+      <c r="Q6" s="6" t="n">
         <v>0.38032588615062</v>
       </c>
-      <c r="R6" s="5" t="n">
+      <c r="R6" s="6" t="n">
         <v>0.960480570395362</v>
       </c>
-      <c r="S6" s="5" t="n">
+      <c r="S6" s="6" t="n">
         <v>1.3789625710996</v>
       </c>
-      <c r="T6" s="5" t="n">
+      <c r="T6" s="6" t="n">
         <v>1.49779300527168</v>
       </c>
-      <c r="U6" s="5" t="n">
+      <c r="U6" s="6" t="n">
         <v>1.52224757753993</v>
       </c>
-      <c r="V6" s="5" t="n">
+      <c r="V6" s="6" t="n">
         <v>1.52848251633768</v>
       </c>
-      <c r="W6" s="5" t="n">
+      <c r="W6" s="6" t="n">
         <v>30.7075919678155</v>
       </c>
-      <c r="X6" s="5" t="n">
+      <c r="X6" s="6" t="n">
         <v>5.70592449027593</v>
       </c>
-      <c r="Y6" s="5" t="n">
+      <c r="Y6" s="6" t="n">
         <v>0.950987415045988</v>
       </c>
-      <c r="Z6" s="5" t="n">
+      <c r="Z6" s="6" t="n">
         <v>1.54846608236749</v>
       </c>
-      <c r="AA6" s="5" t="n">
+      <c r="AA6" s="6" t="n">
         <v>-1.45153391763251</v>
       </c>
-      <c r="AB6" s="5" t="n">
+      <c r="AB6" s="6" t="n">
         <v>2.86878935917656</v>
       </c>
-      <c r="AC6" s="5" t="n">
+      <c r="AC6" s="6" t="n">
         <v>0.999690211611604</v>
       </c>
-      <c r="AD6" s="5" t="n">
+      <c r="AD6" s="6" t="n">
         <v>0.00030978838839625</v>
       </c>
-      <c r="AE6" s="5" t="n">
+      <c r="AE6" s="6" t="n">
         <v>-0.000740609666658486</v>
       </c>
-      <c r="AF6" s="5" t="n">
+      <c r="AF6" s="6" t="n">
         <v>3.29505335275834</v>
       </c>
-      <c r="AG6" s="5" t="n">
+      <c r="AG6" s="6" t="n">
         <v>-2.692412097524E-005</v>
       </c>
-      <c r="AH6" s="5" t="n">
+      <c r="AH6" s="6" t="n">
         <v>0.00763626347939761</v>
       </c>
-      <c r="AI6" s="5" t="n">
+      <c r="AI6" s="6" t="n">
         <v>0.0873857208261504</v>
       </c>
-      <c r="AJ6" s="5" t="n">
+      <c r="AJ6" s="6" t="n">
         <v>-325.744628878758</v>
       </c>
-      <c r="AK6" s="5" t="n">
+      <c r="AK6" s="6" t="n">
         <v>34746.1395609747</v>
       </c>
-      <c r="AL6" s="5" t="n">
+      <c r="AL6" s="6" t="n">
         <v>-0.632018553516278</v>
       </c>
-      <c r="AM6" s="5" t="n">
+      <c r="AM6" s="6" t="n">
         <v>0.0077047532119205</v>
       </c>
-      <c r="AN6" s="5" t="n">
+      <c r="AN6" s="6" t="n">
         <v>0.638084794679147</v>
       </c>
-      <c r="AO6" s="5" t="n">
+      <c r="AO6" s="6" t="n">
         <v>0.0490769143806824</v>
       </c>
-      <c r="AP6" s="5" t="n">
+      <c r="AP6" s="6" t="n">
         <v>0.00522772067917707</v>
       </c>
-      <c r="AQ6" s="5" t="n">
+      <c r="AQ6" s="6" t="n">
         <v>0.749332332145842</v>
       </c>
-      <c r="AR6" s="5" t="n">
+      <c r="AR6" s="6" t="n">
         <v>0.0873857208261504</v>
       </c>
-      <c r="AS6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" s="5" t="n">
+      <c r="AS6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="6" t="n">
         <v>0.632020569072016</v>
       </c>
-      <c r="AV6" s="5" t="n">
+      <c r="AV6" s="6" t="n">
         <v>0.00770220547061568</v>
       </c>
-      <c r="AW6" s="5" t="n">
+      <c r="AW6" s="6" t="n">
         <v>1.29332806100388</v>
       </c>
-      <c r="AX6" s="5" t="n">
+      <c r="AX6" s="6" t="n">
         <v>0.638084794679148</v>
       </c>
-      <c r="AY6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" s="5" t="n">
+      <c r="AY6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="6" t="n">
         <v>0.516170318269996</v>
       </c>
-      <c r="BB6" s="5" t="n">
+      <c r="BB6" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="BC6" s="5" t="n">
+      <c r="BC6" s="6" t="n">
         <v>1.0260997233144</v>
       </c>
-      <c r="BD6" s="5" t="n">
+      <c r="BD6" s="6" t="n">
         <v>515.114070661383</v>
       </c>
-      <c r="BE6" s="5" t="n">
+      <c r="BE6" s="6" t="n">
         <v>324.033862281594</v>
       </c>
-      <c r="BF6" s="5" t="n">
+      <c r="BF6" s="6" t="n">
         <v>1.81890122787219</v>
       </c>
-      <c r="BG6" s="5" t="n">
+      <c r="BG6" s="6" t="n">
         <v>0.999289369883526</v>
       </c>
-      <c r="BH6" s="5" t="n">
+      <c r="BH6" s="6" t="n">
         <v>0.217374029280879</v>
       </c>
-      <c r="BI6" s="5" t="n">
+      <c r="BI6" s="6" t="n">
         <v>7.34895421753302</v>
       </c>
-      <c r="BJ6" s="5" t="n">
+      <c r="BJ6" s="6" t="n">
         <v>0.251489352984297</v>
       </c>
       <c r="BK6" s="6" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="7" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>1024</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <v>102400</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="6" t="n">
         <v>0.786663712457455</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="6" t="n">
         <v>0.205711869945726</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="K7" s="6" t="n">
         <v>0.908048273189851</v>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="L7" s="6" t="n">
         <v>84434.0906437704</v>
       </c>
-      <c r="M7" s="5" t="n">
+      <c r="M7" s="6" t="n">
         <v>1.37472380424615</v>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="N7" s="6" t="n">
         <v>0.000784956356781551</v>
       </c>
-      <c r="O7" s="5" t="n">
+      <c r="O7" s="6" t="n">
         <v>0.021842029934667</v>
       </c>
-      <c r="P7" s="5" t="n">
+      <c r="P7" s="6" t="n">
         <v>0.0632779256846375</v>
       </c>
-      <c r="Q7" s="5" t="n">
+      <c r="Q7" s="6" t="n">
         <v>0.332910598177413</v>
       </c>
-      <c r="R7" s="5" t="n">
+      <c r="R7" s="6" t="n">
         <v>0.903255151612188</v>
       </c>
-      <c r="S7" s="5" t="n">
+      <c r="S7" s="6" t="n">
         <v>1.22946750918002</v>
       </c>
-      <c r="T7" s="5" t="n">
+      <c r="T7" s="6" t="n">
         <v>1.30252014722484</v>
       </c>
-      <c r="U7" s="5" t="n">
+      <c r="U7" s="6" t="n">
         <v>1.32219873237668</v>
       </c>
-      <c r="V7" s="5" t="n">
+      <c r="V7" s="6" t="n">
         <v>1.37393884788937</v>
       </c>
-      <c r="W7" s="5" t="n">
+      <c r="W7" s="6" t="n">
         <v>64.8673988286997</v>
       </c>
-      <c r="X7" s="5" t="n">
+      <c r="X7" s="6" t="n">
         <v>5.66087161448483</v>
       </c>
-      <c r="Y7" s="5" t="n">
+      <c r="Y7" s="6" t="n">
         <v>0.943478602414138</v>
       </c>
-      <c r="Z7" s="5" t="n">
+      <c r="Z7" s="6" t="n">
         <v>1.57225698601445</v>
       </c>
-      <c r="AA7" s="5" t="n">
+      <c r="AA7" s="6" t="n">
         <v>-1.42774301398555</v>
       </c>
-      <c r="AB7" s="5" t="n">
+      <c r="AB7" s="6" t="n">
         <v>0.788659797069141</v>
       </c>
-      <c r="AC7" s="5" t="n">
+      <c r="AC7" s="6" t="n">
         <v>0.999169699798908</v>
       </c>
-      <c r="AD7" s="5" t="n">
+      <c r="AD7" s="6" t="n">
         <v>0.000830300201092083</v>
       </c>
-      <c r="AE7" s="5" t="n">
+      <c r="AE7" s="6" t="n">
         <v>-0.0487255151801592</v>
       </c>
-      <c r="AF7" s="5" t="n">
+      <c r="AF7" s="6" t="n">
         <v>6.71487246115127</v>
       </c>
-      <c r="AG7" s="5" t="n">
+      <c r="AG7" s="6" t="n">
         <v>-0.00117728675394538</v>
       </c>
-      <c r="AH7" s="5" t="n">
+      <c r="AH7" s="6" t="n">
         <v>0.0921826389780251</v>
       </c>
-      <c r="AI7" s="5" t="n">
+      <c r="AI7" s="6" t="n">
         <v>0.303618222414476</v>
       </c>
-      <c r="AJ7" s="5" t="n">
+      <c r="AJ7" s="6" t="n">
         <v>-314.838763774138</v>
       </c>
-      <c r="AK7" s="5" t="n">
+      <c r="AK7" s="6" t="n">
         <v>33259.1924108041</v>
       </c>
-      <c r="AL7" s="5" t="n">
+      <c r="AL7" s="6" t="n">
         <v>-0.622187548772336</v>
       </c>
-      <c r="AM7" s="5" t="n">
+      <c r="AM7" s="6" t="n">
         <v>0.0982097548179268</v>
       </c>
-      <c r="AN7" s="5" t="n">
+      <c r="AN7" s="6" t="n">
         <v>0.696654218867047</v>
       </c>
-      <c r="AO7" s="5" t="n">
+      <c r="AO7" s="6" t="n">
         <v>0.100049663233653</v>
       </c>
-      <c r="AP7" s="5" t="n">
+      <c r="AP7" s="6" t="n">
         <v>0.0821740898689587</v>
       </c>
-      <c r="AQ7" s="5" t="n">
+      <c r="AQ7" s="6" t="n">
         <v>3.13993226415997</v>
       </c>
-      <c r="AR7" s="5" t="n">
+      <c r="AR7" s="6" t="n">
         <v>0.303618222414476</v>
       </c>
-      <c r="AS7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" s="5" t="n">
+      <c r="AS7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="6" t="n">
         <v>0.658001728125113</v>
       </c>
-      <c r="AV7" s="5" t="n">
+      <c r="AV7" s="6" t="n">
         <v>0.052360826449621</v>
       </c>
-      <c r="AW7" s="5" t="n">
+      <c r="AW7" s="6" t="n">
         <v>3.14145422794466</v>
       </c>
-      <c r="AX7" s="5" t="n">
+      <c r="AX7" s="6" t="n">
         <v>0.696654218867048</v>
       </c>
-      <c r="AY7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" s="5" t="n">
+      <c r="AY7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="6" t="n">
         <v>0.435814813711869</v>
       </c>
-      <c r="BB7" s="5" t="n">
+      <c r="BB7" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="BC7" s="5" t="n">
+      <c r="BC7" s="6" t="n">
         <v>0.824551666443071</v>
       </c>
-      <c r="BD7" s="5" t="n">
+      <c r="BD7" s="6" t="n">
         <v>541.232753323826</v>
       </c>
-      <c r="BE7" s="5" t="n">
+      <c r="BE7" s="6" t="n">
         <v>290.427727964314</v>
       </c>
-      <c r="BF7" s="5" t="n">
+      <c r="BF7" s="6" t="n">
         <v>2.01646737950809</v>
       </c>
-      <c r="BG7" s="5" t="n">
+      <c r="BG7" s="6" t="n">
         <v>0.998983521080142</v>
       </c>
-      <c r="BH7" s="5" t="n">
+      <c r="BH7" s="6" t="n">
         <v>0.248703339724769</v>
       </c>
-      <c r="BI7" s="5" t="n">
+      <c r="BI7" s="6" t="n">
         <v>8.42675163408873</v>
       </c>
-      <c r="BJ7" s="5" t="n">
+      <c r="BJ7" s="6" t="n">
         <v>0.250313319516132</v>
       </c>
       <c r="BK7" s="6" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="8" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+    <row r="8" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
         <v>1024</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="6" t="n">
         <v>102400</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I8" s="6" t="n">
         <v>0.786396579940112</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J8" s="6" t="n">
         <v>0.205646087283512</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="K8" s="6" t="n">
         <v>0.907780627808843</v>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="L8" s="6" t="n">
         <v>84384.3244262417</v>
       </c>
-      <c r="M8" s="5" t="n">
+      <c r="M8" s="6" t="n">
         <v>1.36144136056049</v>
       </c>
-      <c r="N8" s="5" t="n">
+      <c r="N8" s="6" t="n">
         <v>0.000270529728315641</v>
       </c>
-      <c r="O8" s="5" t="n">
+      <c r="O8" s="6" t="n">
         <v>0.0218061826719591</v>
       </c>
-      <c r="P8" s="5" t="n">
+      <c r="P8" s="6" t="n">
         <v>0.0630626447484794</v>
       </c>
-      <c r="Q8" s="5" t="n">
+      <c r="Q8" s="6" t="n">
         <v>0.333003474777217</v>
       </c>
-      <c r="R8" s="5" t="n">
+      <c r="R8" s="6" t="n">
         <v>0.903084299167003</v>
       </c>
-      <c r="S8" s="5" t="n">
+      <c r="S8" s="6" t="n">
         <v>1.22888792792566</v>
       </c>
-      <c r="T8" s="5" t="n">
+      <c r="T8" s="6" t="n">
         <v>1.30233092215608</v>
       </c>
-      <c r="U8" s="5" t="n">
+      <c r="U8" s="6" t="n">
         <v>1.32180509361181</v>
       </c>
-      <c r="V8" s="5" t="n">
+      <c r="V8" s="6" t="n">
         <v>1.36117083083217</v>
       </c>
-      <c r="W8" s="5" t="n">
+      <c r="W8" s="6" t="n">
         <v>74.0356788470153</v>
       </c>
-      <c r="X8" s="5" t="n">
+      <c r="X8" s="6" t="n">
         <v>5.67453177844153</v>
       </c>
-      <c r="Y8" s="5" t="n">
+      <c r="Y8" s="6" t="n">
         <v>0.945755296406921</v>
       </c>
-      <c r="Z8" s="5" t="n">
+      <c r="Z8" s="6" t="n">
         <v>1.57204187000813</v>
       </c>
-      <c r="AA8" s="5" t="n">
+      <c r="AA8" s="6" t="n">
         <v>-1.42795812999187</v>
       </c>
-      <c r="AB8" s="5" t="n">
+      <c r="AB8" s="6" t="n">
         <v>0.953913904815882</v>
       </c>
-      <c r="AC8" s="5" t="n">
+      <c r="AC8" s="6" t="n">
         <v>0.999079207612033</v>
       </c>
-      <c r="AD8" s="5" t="n">
+      <c r="AD8" s="6" t="n">
         <v>0.00092079238796688</v>
       </c>
-      <c r="AE8" s="5" t="n">
+      <c r="AE8" s="6" t="n">
         <v>-0.0935581610045037</v>
       </c>
-      <c r="AF8" s="5" t="n">
+      <c r="AF8" s="6" t="n">
         <v>6.63848902322837</v>
       </c>
-      <c r="AG8" s="5" t="n">
+      <c r="AG8" s="6" t="n">
         <v>-0.00187313891486762</v>
       </c>
-      <c r="AH8" s="5" t="n">
+      <c r="AH8" s="6" t="n">
         <v>0.0920883567943728</v>
       </c>
-      <c r="AI8" s="5" t="n">
+      <c r="AI8" s="6" t="n">
         <v>0.303466415676871</v>
       </c>
-      <c r="AJ8" s="5" t="n">
+      <c r="AJ8" s="6" t="n">
         <v>-315.022329642419</v>
       </c>
-      <c r="AK8" s="5" t="n">
+      <c r="AK8" s="6" t="n">
         <v>33302.1612057293</v>
       </c>
-      <c r="AL8" s="5" t="n">
+      <c r="AL8" s="6" t="n">
         <v>-0.622499030618212</v>
       </c>
-      <c r="AM8" s="5" t="n">
+      <c r="AM8" s="6" t="n">
         <v>0.0989718491520283</v>
       </c>
-      <c r="AN8" s="5" t="n">
+      <c r="AN8" s="6" t="n">
         <v>0.697478954716658</v>
       </c>
-      <c r="AO8" s="5" t="n">
+      <c r="AO8" s="6" t="n">
         <v>0.100777213042584</v>
       </c>
-      <c r="AP8" s="5" t="n">
+      <c r="AP8" s="6" t="n">
         <v>0.0819358187751367</v>
       </c>
-      <c r="AQ8" s="5" t="n">
+      <c r="AQ8" s="6" t="n">
         <v>3.14050894868783</v>
       </c>
-      <c r="AR8" s="5" t="n">
+      <c r="AR8" s="6" t="n">
         <v>0.303466415676871</v>
       </c>
-      <c r="AS8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" s="5" t="n">
+      <c r="AS8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="6" t="n">
         <v>0.658264180648578</v>
       </c>
-      <c r="AV8" s="5" t="n">
+      <c r="AV8" s="6" t="n">
         <v>0.053165160747699</v>
       </c>
-      <c r="AW8" s="5" t="n">
+      <c r="AW8" s="6" t="n">
         <v>3.14102911598624</v>
       </c>
-      <c r="AX8" s="5" t="n">
+      <c r="AX8" s="6" t="n">
         <v>0.697478954716659</v>
       </c>
-      <c r="AY8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" s="5" t="n">
+      <c r="AY8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="6" t="n">
         <v>0.435598305701647</v>
       </c>
-      <c r="BB8" s="5" t="n">
+      <c r="BB8" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="BC8" s="5" t="n">
+      <c r="BC8" s="6" t="n">
         <v>0.824065668225017</v>
       </c>
-      <c r="BD8" s="5" t="n">
+      <c r="BD8" s="6" t="n">
         <v>541.28291188854</v>
       </c>
-      <c r="BE8" s="5" t="n">
+      <c r="BE8" s="6" t="n">
         <v>290.340618212401</v>
       </c>
-      <c r="BF8" s="5" t="n">
+      <c r="BF8" s="6" t="n">
         <v>1.94440306592081</v>
       </c>
-      <c r="BG8" s="5" t="n">
+      <c r="BG8" s="6" t="n">
         <v>0.998973152384972</v>
       </c>
-      <c r="BH8" s="5" t="n">
+      <c r="BH8" s="6" t="n">
         <v>0.250032924127679</v>
       </c>
-      <c r="BI8" s="5" t="n">
+      <c r="BI8" s="6" t="n">
         <v>8.50259360107585</v>
       </c>
-      <c r="BJ8" s="5" t="n">
+      <c r="BJ8" s="6" t="n">
         <v>0.250573328362839</v>
       </c>
       <c r="BK8" s="6" t="n">
@@ -3740,7 +3744,7 @@
       <c r="BJ15" s="9" t="n">
         <v>0.252464537391765</v>
       </c>
-      <c r="BK15" s="10" t="n">
+      <c r="BK15" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3931,7 +3935,7 @@
       <c r="BJ16" s="9" t="n">
         <v>0.25163172302195</v>
       </c>
-      <c r="BK16" s="10" t="n">
+      <c r="BK16" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4122,7 +4126,7 @@
       <c r="BJ17" s="9" t="n">
         <v>0.251797452699515</v>
       </c>
-      <c r="BK17" s="10" t="n">
+      <c r="BK17" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4313,7 +4317,7 @@
       <c r="BJ18" s="9" t="n">
         <v>0.252320043693763</v>
       </c>
-      <c r="BK18" s="10" t="n">
+      <c r="BK18" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4504,7 +4508,7 @@
       <c r="BJ19" s="9" t="n">
         <v>0.251643818179809</v>
       </c>
-      <c r="BK19" s="10" t="n">
+      <c r="BK19" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4695,227 +4699,230 @@
       <c r="BJ20" s="9" t="n">
         <v>0.251359583243107</v>
       </c>
-      <c r="BK20" s="10" t="n">
+      <c r="BK20" s="9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I21" s="11" t="n">
+      <c r="I21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,I2:I20)</f>
         <v>0.968243503115214</v>
       </c>
-      <c r="J21" s="11" t="n">
+      <c r="J21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,J2:J20)</f>
         <v>0.854773108412023</v>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="K21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,K2:K20)</f>
         <v>0.957160969187776</v>
       </c>
-      <c r="L21" s="11" t="n">
+      <c r="L21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,L2:L20)</f>
         <v>0.901686267133836</v>
       </c>
-      <c r="M21" s="11" t="n">
+      <c r="M21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,M2:M20)</f>
         <v>0.945655340738124</v>
       </c>
-      <c r="N21" s="0" t="n">
+      <c r="N21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,N2:N20)</f>
         <v>0.376696064157676</v>
       </c>
-      <c r="O21" s="0" t="n">
+      <c r="O21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,O2:O20)</f>
         <v>0.374968428219903</v>
       </c>
-      <c r="P21" s="0" t="n">
+      <c r="P21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,P2:P20)</f>
         <v>0.26386146925435</v>
       </c>
-      <c r="Q21" s="11" t="n">
+      <c r="Q21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,Q2:Q20)</f>
         <v>0.886931435109222</v>
       </c>
-      <c r="R21" s="11" t="n">
+      <c r="R21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,R2:R20)</f>
         <v>0.966798957463255</v>
       </c>
-      <c r="S21" s="11" t="n">
+      <c r="S21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,S2:S20)</f>
         <v>0.938711569944745</v>
       </c>
-      <c r="T21" s="12" t="n">
+      <c r="T21" s="11" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,T2:T20)</f>
         <v>0.929794991392683</v>
       </c>
-      <c r="U21" s="12" t="n">
+      <c r="U21" s="11" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,U2:U20)</f>
         <v>0.929309120416535</v>
       </c>
-      <c r="V21" s="11" t="n">
+      <c r="V21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,V2:V20)</f>
         <v>0.929630105281231</v>
       </c>
-      <c r="W21" s="0" t="n">
+      <c r="W21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,W2:W20)</f>
         <v>0.0872903106226156</v>
       </c>
-      <c r="X21" s="0" t="n">
+      <c r="X21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,X2:X20)</f>
         <v>0.165932182659971</v>
       </c>
-      <c r="Y21" s="0" t="n">
+      <c r="Y21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,Y2:Y20)</f>
         <v>0.165932182659971</v>
       </c>
-      <c r="Z21" s="0" t="n">
+      <c r="Z21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,Z2:Z20)</f>
         <v>-0.092287023237424</v>
       </c>
-      <c r="AA21" s="0" t="n">
+      <c r="AA21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AA2:AA20)</f>
         <v>-0.092287023237424</v>
       </c>
-      <c r="AB21" s="0" t="n">
+      <c r="AB21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AB2:AB20)</f>
         <v>0.263129738350481</v>
       </c>
-      <c r="AC21" s="0" t="n">
+      <c r="AC21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AC2:AC20)</f>
         <v>-0.205436000756555</v>
       </c>
-      <c r="AD21" s="0" t="n">
+      <c r="AD21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AD2:AD20)</f>
         <v>0.205436000756564</v>
       </c>
-      <c r="AE21" s="0" t="n">
+      <c r="AE21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AE2:AE20)</f>
         <v>-0.182576071929572</v>
       </c>
-      <c r="AF21" s="0" t="n">
+      <c r="AF21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AF2:AF20)</f>
         <v>0.0335370955739892</v>
       </c>
-      <c r="AG21" s="0" t="n">
+      <c r="AG21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AG2:AG20)</f>
         <v>-0.32515666699282</v>
       </c>
-      <c r="AH21" s="0" t="n">
+      <c r="AH21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AH2:AH20)</f>
         <v>-0.11903922126476</v>
       </c>
-      <c r="AI21" s="0" t="n">
+      <c r="AI21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AI2:AI20)</f>
         <v>-0.134359397727729</v>
       </c>
-      <c r="AJ21" s="0" t="n">
+      <c r="AJ21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AJ2:AJ20)</f>
         <v>0.101581058696087</v>
       </c>
-      <c r="AK21" s="0" t="n">
+      <c r="AK21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AK2:AK20)</f>
         <v>-0.207623115113163</v>
       </c>
-      <c r="AL21" s="0" t="n">
+      <c r="AL21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AL2:AL20)</f>
         <v>-0.00546243986059112</v>
       </c>
-      <c r="AM21" s="0" t="n">
+      <c r="AM21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AM2:AM20)</f>
         <v>-0.121242502097181</v>
       </c>
-      <c r="AN21" s="0" t="n">
+      <c r="AN21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AN2:AN20)</f>
         <v>-0.144168875698711</v>
       </c>
-      <c r="AO21" s="0" t="n">
+      <c r="AO21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AO2:AO20)</f>
         <v>-0.462615048494343</v>
       </c>
-      <c r="AP21" s="0" t="n">
+      <c r="AP21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AP2:AP20)</f>
         <v>-0.049921042378686</v>
       </c>
-      <c r="AQ21" s="0" t="n">
+      <c r="AQ21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AQ2:AQ20)</f>
         <v>-0.190448727112261</v>
       </c>
-      <c r="AR21" s="0" t="n">
+      <c r="AR21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AR2:AR20)</f>
         <v>-0.134359397727729</v>
       </c>
-      <c r="AS21" s="0" t="e">
+      <c r="AS21" s="1" t="e">
         <f aca="false">PEARSON($BK$2:$BK$20,AS2:AS20)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AT21" s="0" t="e">
+      <c r="AT21" s="1" t="e">
         <f aca="false">PEARSON($BK$2:$BK$20,AT2:AT20)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AU21" s="0" t="n">
+      <c r="AU21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AU2:AU20)</f>
         <v>-0.0770799875673555</v>
       </c>
-      <c r="AV21" s="0" t="n">
+      <c r="AV21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AV2:AV20)</f>
         <v>-0.179936238137499</v>
       </c>
-      <c r="AW21" s="0" t="n">
+      <c r="AW21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AW2:AW20)</f>
         <v>-0.243514896455941</v>
       </c>
-      <c r="AX21" s="0" t="n">
+      <c r="AX21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,AX2:AX20)</f>
         <v>-0.144168875698713</v>
       </c>
-      <c r="AY21" s="0" t="e">
+      <c r="AY21" s="1" t="e">
         <f aca="false">PEARSON($BK$2:$BK$20,AY2:AY20)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AZ21" s="0" t="e">
+      <c r="AZ21" s="1" t="e">
         <f aca="false">PEARSON($BK$2:$BK$20,AZ2:AZ20)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="BA21" s="11" t="n">
+      <c r="BA21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,BA2:BA20)</f>
         <v>0.908862254960293</v>
       </c>
-      <c r="BB21" s="11" t="n">
+      <c r="BB21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,BB2:BB20)</f>
         <v>0.85485041426511</v>
       </c>
-      <c r="BC21" s="11" t="n">
+      <c r="BC21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,BC2:BC20)</f>
         <v>0.901686267133836</v>
       </c>
-      <c r="BD21" s="0" t="n">
+      <c r="BD21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,BD2:BD20)</f>
         <v>-0.168921799601214</v>
       </c>
-      <c r="BE21" s="11" t="n">
+      <c r="BE21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,BE2:BE20)</f>
         <v>0.957200286259692</v>
       </c>
-      <c r="BF21" s="11" t="n">
+      <c r="BF21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,BF2:BF20)</f>
         <v>0.904993412382989</v>
       </c>
-      <c r="BG21" s="13" t="n">
+      <c r="BG21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,BG2:BG20)</f>
         <v>0.778271439854199</v>
       </c>
-      <c r="BH21" s="11" t="n">
+      <c r="BH21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,BH2:BH20)</f>
         <v>-0.938349492026157</v>
       </c>
-      <c r="BI21" s="11" t="n">
+      <c r="BI21" s="10" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,BI2:BI20)</f>
         <v>0.926863623722399</v>
       </c>
-      <c r="BJ21" s="0" t="n">
+      <c r="BJ21" s="1" t="n">
         <f aca="false">PEARSON($BK$2:$BK$20,BJ2:BJ20)</f>
         <v>-0.355606291612224</v>
       </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BA30" s="12"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
